--- a/Thesis Forecasting/outputs/xgboost_forecast/Day_Ahead_24H_XGBOOST.xlsx
+++ b/Thesis Forecasting/outputs/xgboost_forecast/Day_Ahead_24H_XGBOOST.xlsx
@@ -21,13 +21,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -451,139 +463,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Hour</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus1_Unit1_MW</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus1_Unit2_MW</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit1_MW</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit2_MW</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus2_Unit3_MW</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit1_MW</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit2_MW</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus4_Unit3_MW</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus5_Unit1_MW</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus5_Unit2_MW</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit1_MW</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit2_MW</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit3_MW</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit4_MW</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus6_Unit5_MW</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus7_Unit1_MW</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Gen_Agus7_Unit2_MW</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus1_MW</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus2_MW</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus4_MW</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus5_MW</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus6_MW</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Total_Gen_Agus7_MW</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Total_Cascade_Generation_MW</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -592,10 +604,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30.66095147258629</v>
+        <v>30.91433560818136</v>
       </c>
       <c r="D2" t="n">
-        <v>29.59841201382588</v>
+        <v>29.84301525289416</v>
       </c>
       <c r="E2" t="n">
         <v>40.2588609705938</v>
@@ -607,19 +619,19 @@
         <v>51.06413777207867</v>
       </c>
       <c r="H2" t="n">
-        <v>47.60980050129717</v>
+        <v>47.73589529905708</v>
       </c>
       <c r="I2" t="n">
-        <v>45.16307755732356</v>
+        <v>45.28269219697429</v>
       </c>
       <c r="J2" t="n">
-        <v>48.16022194093672</v>
+        <v>48.28777453266727</v>
       </c>
       <c r="K2" t="n">
-        <v>21.67467077301761</v>
+        <v>21.92474915323946</v>
       </c>
       <c r="L2" t="n">
-        <v>21.48225183678845</v>
+        <v>21.73011012257841</v>
       </c>
       <c r="M2" t="n">
         <v>34.5</v>
@@ -643,16 +655,16 @@
         <v>20.84046213000656</v>
       </c>
       <c r="T2" t="n">
-        <v>60.25936348641217</v>
+        <v>60.75735086107552</v>
       </c>
       <c r="U2" t="n">
         <v>129.9716</v>
       </c>
       <c r="V2" t="n">
-        <v>140.9330999995574</v>
+        <v>141.3063620286986</v>
       </c>
       <c r="W2" t="n">
-        <v>43.15692260980606</v>
+        <v>43.65485927581787</v>
       </c>
       <c r="X2" t="n">
         <v>158.3225</v>
@@ -661,11 +673,11 @@
         <v>41.92835</v>
       </c>
       <c r="Z2" t="n">
-        <v>574.5718360957757</v>
+        <v>575.941022165592</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -674,10 +686,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.36556688969704</v>
+        <v>30.78639889931165</v>
       </c>
       <c r="D3" t="n">
-        <v>29.43040827259747</v>
+        <v>29.83828005388596</v>
       </c>
       <c r="E3" t="n">
         <v>40.33240941262922</v>
@@ -689,19 +701,19 @@
         <v>51.51274492394714</v>
       </c>
       <c r="H3" t="n">
-        <v>47.56745501792663</v>
+        <v>47.81157837152412</v>
       </c>
       <c r="I3" t="n">
-        <v>45.31066754042637</v>
+        <v>45.54320872030537</v>
       </c>
       <c r="J3" t="n">
-        <v>48.25406845204171</v>
+        <v>48.50171560934276</v>
       </c>
       <c r="K3" t="n">
-        <v>21.19826765298087</v>
+        <v>21.56315781231261</v>
       </c>
       <c r="L3" t="n">
-        <v>21.17423965216439</v>
+        <v>21.5387162125554</v>
       </c>
       <c r="M3" t="n">
         <v>34.5</v>
@@ -725,16 +737,16 @@
         <v>20.91599189842184</v>
       </c>
       <c r="T3" t="n">
-        <v>59.79597516229451</v>
+        <v>60.6246789531976</v>
       </c>
       <c r="U3" t="n">
         <v>129.9716</v>
       </c>
       <c r="V3" t="n">
-        <v>141.1321910103947</v>
+        <v>141.8565027011722</v>
       </c>
       <c r="W3" t="n">
-        <v>42.37250730514526</v>
+        <v>43.10187402486801</v>
       </c>
       <c r="X3" t="n">
         <v>156.04105</v>
@@ -743,11 +755,11 @@
         <v>42.14252500000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>571.4558484778344</v>
+        <v>573.7382306792377</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -756,10 +768,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30.81718967355396</v>
+        <v>31.00286395667048</v>
       </c>
       <c r="D4" t="n">
-        <v>29.89406112980854</v>
+        <v>30.0741735420212</v>
       </c>
       <c r="E4" t="n">
         <v>40.47405329288873</v>
@@ -771,19 +783,19 @@
         <v>51.67759607429286</v>
       </c>
       <c r="H4" t="n">
-        <v>47.5410338407282</v>
+        <v>47.90717935496485</v>
       </c>
       <c r="I4" t="n">
-        <v>45.3814499425169</v>
+        <v>45.7309630469579</v>
       </c>
       <c r="J4" t="n">
-        <v>48.29707143055649</v>
+        <v>48.66903969936422</v>
       </c>
       <c r="K4" t="n">
-        <v>21.31913350879304</v>
+        <v>21.78727550101956</v>
       </c>
       <c r="L4" t="n">
-        <v>21.38141612470992</v>
+        <v>21.85092576669971</v>
       </c>
       <c r="M4" t="n">
         <v>34.5</v>
@@ -807,16 +819,16 @@
         <v>21.90691455486583</v>
       </c>
       <c r="T4" t="n">
-        <v>60.7112508033625</v>
+        <v>61.07703749869168</v>
       </c>
       <c r="U4" t="n">
         <v>129.9716</v>
       </c>
       <c r="V4" t="n">
-        <v>141.2195552138016</v>
+        <v>142.307182101287</v>
       </c>
       <c r="W4" t="n">
-        <v>42.70054963350296</v>
+        <v>43.63820126771927</v>
       </c>
       <c r="X4" t="n">
         <v>157.527625</v>
@@ -825,11 +837,11 @@
         <v>44.1821125</v>
       </c>
       <c r="Z4" t="n">
-        <v>576.312693150667</v>
+        <v>578.703758367698</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -838,34 +850,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30.55844138556749</v>
+        <v>31.11607628692085</v>
       </c>
       <c r="D5" t="n">
-        <v>29.6619598573912</v>
+        <v>30.20323563289052</v>
       </c>
       <c r="E5" t="n">
-        <v>40.53966881175823</v>
+        <v>40.53966881175825</v>
       </c>
       <c r="F5" t="n">
-        <v>37.68909958966154</v>
+        <v>37.68909958966155</v>
       </c>
       <c r="G5" t="n">
-        <v>51.74283159858019</v>
+        <v>51.7428315985802</v>
       </c>
       <c r="H5" t="n">
-        <v>47.57722503663441</v>
+        <v>48.061087940654</v>
       </c>
       <c r="I5" t="n">
-        <v>45.46433308241247</v>
+        <v>45.92670776310541</v>
       </c>
       <c r="J5" t="n">
-        <v>48.37136997404232</v>
+        <v>48.86330937422852</v>
       </c>
       <c r="K5" t="n">
-        <v>21.45834949130081</v>
+        <v>22.03815968773327</v>
       </c>
       <c r="L5" t="n">
-        <v>21.5620614350412</v>
+        <v>22.14467395522633</v>
       </c>
       <c r="M5" t="n">
         <v>34.5</v>
@@ -874,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>47.61289949852956</v>
+        <v>47.61289949852959</v>
       </c>
       <c r="P5" t="n">
-        <v>25.75461300147042</v>
+        <v>25.75461300147043</v>
       </c>
       <c r="Q5" t="n">
         <v>50</v>
@@ -889,16 +901,16 @@
         <v>22.49639498843253</v>
       </c>
       <c r="T5" t="n">
-        <v>60.22040124295869</v>
+        <v>61.31931191981137</v>
       </c>
       <c r="U5" t="n">
         <v>129.9716</v>
       </c>
       <c r="V5" t="n">
-        <v>141.4129280930892</v>
+        <v>142.8511050779879</v>
       </c>
       <c r="W5" t="n">
-        <v>43.02041092634201</v>
+        <v>44.18283364295959</v>
       </c>
       <c r="X5" t="n">
         <v>157.8675125</v>
@@ -907,11 +919,11 @@
         <v>45.37730625</v>
       </c>
       <c r="Z5" t="n">
-        <v>577.8701590123899</v>
+        <v>581.5696693907589</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -920,34 +932,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30.71048854478132</v>
+        <v>31.17455593920187</v>
       </c>
       <c r="D6" t="n">
-        <v>29.78575314239266</v>
+        <v>30.23584682395321</v>
       </c>
       <c r="E6" t="n">
-        <v>40.57726522972612</v>
+        <v>40.57726522972613</v>
       </c>
       <c r="F6" t="n">
-        <v>37.60768300104471</v>
+        <v>37.60768300104473</v>
       </c>
       <c r="G6" t="n">
-        <v>51.78665176922912</v>
+        <v>51.78665176922914</v>
       </c>
       <c r="H6" t="n">
-        <v>47.58472974008171</v>
+        <v>48.18118984002477</v>
       </c>
       <c r="I6" t="n">
-        <v>45.49516742316315</v>
+        <v>46.0654354956387</v>
       </c>
       <c r="J6" t="n">
-        <v>48.39266210345355</v>
+        <v>48.99924938959344</v>
       </c>
       <c r="K6" t="n">
-        <v>21.56476315069478</v>
+        <v>22.12331615099435</v>
       </c>
       <c r="L6" t="n">
-        <v>21.69429969203193</v>
+        <v>22.2562078427362</v>
       </c>
       <c r="M6" t="n">
         <v>34.5</v>
@@ -956,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>48.31246961784987</v>
+        <v>48.31246961784986</v>
       </c>
       <c r="P6" t="n">
-        <v>25.01253663215014</v>
+        <v>25.01253663215013</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -971,16 +983,16 @@
         <v>22.83347961792889</v>
       </c>
       <c r="T6" t="n">
-        <v>60.49624168717398</v>
+        <v>61.41040276315509</v>
       </c>
       <c r="U6" t="n">
         <v>129.9716</v>
       </c>
       <c r="V6" t="n">
-        <v>141.4725592666984</v>
+        <v>143.2458747252569</v>
       </c>
       <c r="W6" t="n">
-        <v>43.25906284272671</v>
+        <v>44.37952399373054</v>
       </c>
       <c r="X6" t="n">
         <v>157.82500625</v>
@@ -989,11 +1001,11 @@
         <v>46.069903125</v>
       </c>
       <c r="Z6" t="n">
-        <v>579.094373171599</v>
+        <v>582.9023108571425</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1002,34 +1014,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.31309273679822</v>
+        <v>31.0542354379348</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46062076300546</v>
+        <v>30.18092087355631</v>
       </c>
       <c r="E7" t="n">
-        <v>40.48299959464392</v>
+        <v>40.48299959464393</v>
       </c>
       <c r="F7" t="n">
-        <v>37.62379444748177</v>
+        <v>37.62379444748178</v>
       </c>
       <c r="G7" t="n">
-        <v>51.86480595787427</v>
+        <v>51.86480595787428</v>
       </c>
       <c r="H7" t="n">
-        <v>47.57052337820553</v>
+        <v>48.28393417591501</v>
       </c>
       <c r="I7" t="n">
-        <v>45.49750017708251</v>
+        <v>46.17982203503353</v>
       </c>
       <c r="J7" t="n">
-        <v>48.39107046440365</v>
+        <v>49.11678693187987</v>
       </c>
       <c r="K7" t="n">
-        <v>21.46381407970068</v>
+        <v>22.14550758212528</v>
       </c>
       <c r="L7" t="n">
-        <v>21.59358216947439</v>
+        <v>22.27939712316075</v>
       </c>
       <c r="M7" t="n">
         <v>34.5</v>
@@ -1041,7 +1053,7 @@
         <v>48.70607997557301</v>
       </c>
       <c r="P7" t="n">
-        <v>24.29267314942698</v>
+        <v>24.29267314942699</v>
       </c>
       <c r="Q7" t="n">
         <v>50</v>
@@ -1053,16 +1065,16 @@
         <v>22.30765899100898</v>
       </c>
       <c r="T7" t="n">
-        <v>59.77371349980368</v>
+        <v>61.23515631149111</v>
       </c>
       <c r="U7" t="n">
         <v>129.9716</v>
       </c>
       <c r="V7" t="n">
-        <v>141.4590940196917</v>
+        <v>143.5805431428284</v>
       </c>
       <c r="W7" t="n">
-        <v>43.05739624917507</v>
+        <v>44.42490470528602</v>
       </c>
       <c r="X7" t="n">
         <v>157.498753125</v>
@@ -1071,11 +1083,11 @@
         <v>45.01120156250001</v>
       </c>
       <c r="Z7" t="n">
-        <v>576.7717584561705</v>
+        <v>581.7221588471054</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1084,10 +1096,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30.27920110088346</v>
+        <v>30.84916465063833</v>
       </c>
       <c r="D8" t="n">
-        <v>29.42743679045216</v>
+        <v>29.98136707009827</v>
       </c>
       <c r="E8" t="n">
         <v>40.39242388841581</v>
@@ -1096,22 +1108,22 @@
         <v>37.63550649093683</v>
       </c>
       <c r="G8" t="n">
-        <v>51.94366962064733</v>
+        <v>51.94366962064734</v>
       </c>
       <c r="H8" t="n">
-        <v>47.58380900986369</v>
+        <v>47.98227189432207</v>
       </c>
       <c r="I8" t="n">
-        <v>45.52213917697092</v>
+        <v>45.9033378086192</v>
       </c>
       <c r="J8" t="n">
-        <v>48.41554724781621</v>
+        <v>48.82097503954675</v>
       </c>
       <c r="K8" t="n">
-        <v>20.74380689527041</v>
+        <v>21.40616156984609</v>
       </c>
       <c r="L8" t="n">
-        <v>20.80955233131402</v>
+        <v>21.47400627325732</v>
       </c>
       <c r="M8" t="n">
         <v>34.5</v>
@@ -1123,7 +1135,7 @@
         <v>49.37897687737681</v>
       </c>
       <c r="P8" t="n">
-        <v>23.81494968512317</v>
+        <v>23.81494968512318</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
@@ -1135,16 +1147,16 @@
         <v>20.11161628107959</v>
       </c>
       <c r="T8" t="n">
-        <v>59.70663789133562</v>
+        <v>60.83053172073659</v>
       </c>
       <c r="U8" t="n">
         <v>129.9716</v>
       </c>
       <c r="V8" t="n">
-        <v>141.5214954346508</v>
+        <v>142.706584742488</v>
       </c>
       <c r="W8" t="n">
-        <v>41.55335922658443</v>
+        <v>42.88016784310341</v>
       </c>
       <c r="X8" t="n">
         <v>157.6939265625</v>
@@ -1153,11 +1165,11 @@
         <v>40.58645078125</v>
       </c>
       <c r="Z8" t="n">
-        <v>571.0334698963209</v>
+        <v>574.6692616500781</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1166,34 +1178,34 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30.39025979300672</v>
+        <v>30.80946611318138</v>
       </c>
       <c r="D9" t="n">
-        <v>29.53108568411669</v>
+        <v>29.93844046965392</v>
       </c>
       <c r="E9" t="n">
-        <v>40.32825151309162</v>
+        <v>40.32825151309163</v>
       </c>
       <c r="F9" t="n">
         <v>37.65644011242598</v>
       </c>
       <c r="G9" t="n">
-        <v>51.98690837448235</v>
+        <v>51.98690837448238</v>
       </c>
       <c r="H9" t="n">
-        <v>47.59731525022811</v>
+        <v>47.6909601219564</v>
       </c>
       <c r="I9" t="n">
-        <v>45.54333986181577</v>
+        <v>45.63294365978246</v>
       </c>
       <c r="J9" t="n">
-        <v>48.43603696652422</v>
+        <v>48.53133197307893</v>
       </c>
       <c r="K9" t="n">
-        <v>21.29304703218894</v>
+        <v>22.02089628764712</v>
       </c>
       <c r="L9" t="n">
-        <v>21.3386948056702</v>
+        <v>22.06810441544927</v>
       </c>
       <c r="M9" t="n">
         <v>34.5</v>
@@ -1217,16 +1229,16 @@
         <v>19.82533199560491</v>
       </c>
       <c r="T9" t="n">
-        <v>59.9213454771234</v>
+        <v>60.74790658283529</v>
       </c>
       <c r="U9" t="n">
         <v>129.9716</v>
       </c>
       <c r="V9" t="n">
-        <v>141.5766920785681</v>
+        <v>141.8552357548178</v>
       </c>
       <c r="W9" t="n">
-        <v>42.63174183785915</v>
+        <v>44.08900070309639</v>
       </c>
       <c r="X9" t="n">
         <v>158.03151328125</v>
@@ -1235,11 +1247,11 @@
         <v>39.98407539062501</v>
       </c>
       <c r="Z9" t="n">
-        <v>572.1169680654256</v>
+        <v>574.6793317126245</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1248,34 +1260,34 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30.33739571588971</v>
+        <v>30.70217813859473</v>
       </c>
       <c r="D10" t="n">
-        <v>29.50352643498793</v>
+        <v>29.85828226017761</v>
       </c>
       <c r="E10" t="n">
-        <v>40.31090614286467</v>
+        <v>40.31090614286469</v>
       </c>
       <c r="F10" t="n">
-        <v>37.64147643066629</v>
+        <v>37.64147643066631</v>
       </c>
       <c r="G10" t="n">
-        <v>52.01921742646899</v>
+        <v>52.01921742646901</v>
       </c>
       <c r="H10" t="n">
-        <v>47.6366669054835</v>
+        <v>47.87253253455204</v>
       </c>
       <c r="I10" t="n">
-        <v>45.56919502987426</v>
+        <v>45.79482388995371</v>
       </c>
       <c r="J10" t="n">
-        <v>48.47160508435523</v>
+        <v>48.71160478139254</v>
       </c>
       <c r="K10" t="n">
-        <v>21.60001071422969</v>
+        <v>21.98023117929008</v>
       </c>
       <c r="L10" t="n">
-        <v>21.57535069674577</v>
+        <v>21.95513707668277</v>
       </c>
       <c r="M10" t="n">
         <v>34.5</v>
@@ -1299,16 +1311,16 @@
         <v>21.07555768297193</v>
       </c>
       <c r="T10" t="n">
-        <v>59.84092215087763</v>
+        <v>60.56046039877234</v>
       </c>
       <c r="U10" t="n">
         <v>129.9716</v>
       </c>
       <c r="V10" t="n">
-        <v>141.677467019713</v>
+        <v>142.3789612058983</v>
       </c>
       <c r="W10" t="n">
-        <v>43.17536141097546</v>
+        <v>43.93536825597286</v>
       </c>
       <c r="X10" t="n">
         <v>157.807006640625</v>
@@ -1317,11 +1329,11 @@
         <v>42.6328376953125</v>
       </c>
       <c r="Z10" t="n">
-        <v>575.1051949175035</v>
+        <v>577.2862341965811</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1330,34 +1342,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30.22130812563747</v>
+        <v>30.49478576214693</v>
       </c>
       <c r="D11" t="n">
-        <v>29.41729577774225</v>
+        <v>29.68349777298189</v>
       </c>
       <c r="E11" t="n">
-        <v>40.30634245574818</v>
+        <v>40.30634245574819</v>
       </c>
       <c r="F11" t="n">
-        <v>37.62763226357112</v>
+        <v>37.62763226357113</v>
       </c>
       <c r="G11" t="n">
-        <v>52.03762528068067</v>
+        <v>52.03762528068068</v>
       </c>
       <c r="H11" t="n">
-        <v>47.71287687231924</v>
+        <v>48.06517429399553</v>
       </c>
       <c r="I11" t="n">
-        <v>45.62940653762703</v>
+        <v>45.96632024582456</v>
       </c>
       <c r="J11" t="n">
-        <v>48.53850566562661</v>
+        <v>48.89689928007539</v>
       </c>
       <c r="K11" t="n">
-        <v>21.41310774797144</v>
+        <v>22.14792739500034</v>
       </c>
       <c r="L11" t="n">
-        <v>21.36310385769663</v>
+        <v>22.09620755384934</v>
       </c>
       <c r="M11" t="n">
         <v>34.5</v>
@@ -1381,16 +1393,16 @@
         <v>21.68893945519304</v>
       </c>
       <c r="T11" t="n">
-        <v>59.63860390337972</v>
+        <v>60.17828353512881</v>
       </c>
       <c r="U11" t="n">
         <v>129.9716</v>
       </c>
       <c r="V11" t="n">
-        <v>141.8807890755729</v>
+        <v>142.9283938198955</v>
       </c>
       <c r="W11" t="n">
-        <v>42.77621160566807</v>
+        <v>44.24413494884968</v>
       </c>
       <c r="X11" t="n">
         <v>157.6656033203125</v>
@@ -1399,11 +1411,11 @@
         <v>43.87351884765625</v>
       </c>
       <c r="Z11" t="n">
-        <v>575.8063267525893</v>
+        <v>578.8615344718427</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1412,34 +1424,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.19213213993407</v>
+        <v>30.73908886515053</v>
       </c>
       <c r="D12" t="n">
-        <v>29.39694031448534</v>
+        <v>29.92949144837918</v>
       </c>
       <c r="E12" t="n">
-        <v>40.30594173893524</v>
+        <v>40.30594173893525</v>
       </c>
       <c r="F12" t="n">
-        <v>37.6256360440225</v>
+        <v>37.62563604402251</v>
       </c>
       <c r="G12" t="n">
         <v>52.04002221704224</v>
       </c>
       <c r="H12" t="n">
-        <v>47.77481593320876</v>
+        <v>48.25964217113603</v>
       </c>
       <c r="I12" t="n">
-        <v>45.6853169385188</v>
+        <v>46.14893861674322</v>
       </c>
       <c r="J12" t="n">
-        <v>48.59322614556847</v>
+        <v>49.08635773719704</v>
       </c>
       <c r="K12" t="n">
-        <v>21.36487773257095</v>
+        <v>22.20172931627904</v>
       </c>
       <c r="L12" t="n">
-        <v>21.29411847812336</v>
+        <v>22.1281984571966</v>
       </c>
       <c r="M12" t="n">
         <v>34.5</v>
@@ -1463,16 +1475,16 @@
         <v>21.88724830372933</v>
       </c>
       <c r="T12" t="n">
-        <v>59.58907245441942</v>
+        <v>60.66858031352972</v>
       </c>
       <c r="U12" t="n">
         <v>129.9716</v>
       </c>
       <c r="V12" t="n">
-        <v>142.053359017296</v>
+        <v>143.4949385250763</v>
       </c>
       <c r="W12" t="n">
-        <v>42.65899621069431</v>
+        <v>44.32992777347565</v>
       </c>
       <c r="X12" t="n">
         <v>157.7282016601562</v>
@@ -1481,11 +1493,11 @@
         <v>44.41135942382813</v>
       </c>
       <c r="Z12" t="n">
-        <v>576.412588766394</v>
+        <v>580.6046076960661</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1494,13 +1506,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30.31970761461307</v>
+        <v>30.62743974171508</v>
       </c>
       <c r="D13" t="n">
-        <v>29.54763925731994</v>
+        <v>29.8475352192162</v>
       </c>
       <c r="E13" t="n">
-        <v>40.31065176990717</v>
+        <v>40.31065176990718</v>
       </c>
       <c r="F13" t="n">
         <v>37.63130939843649</v>
@@ -1509,19 +1521,19 @@
         <v>52.02963883165631</v>
       </c>
       <c r="H13" t="n">
-        <v>47.8314973981704</v>
+        <v>48.44143227564274</v>
       </c>
       <c r="I13" t="n">
-        <v>45.73730711303886</v>
+        <v>46.3205374179085</v>
       </c>
       <c r="J13" t="n">
-        <v>48.63819227210381</v>
+        <v>49.25841391386025</v>
       </c>
       <c r="K13" t="n">
-        <v>21.33820773282518</v>
+        <v>22.30459092833075</v>
       </c>
       <c r="L13" t="n">
-        <v>21.26695333174</v>
+        <v>22.23010949634042</v>
       </c>
       <c r="M13" t="n">
         <v>34.5</v>
@@ -1545,16 +1557,16 @@
         <v>21.86071397289049</v>
       </c>
       <c r="T13" t="n">
-        <v>59.86734687193302</v>
+        <v>60.47497496093128</v>
       </c>
       <c r="U13" t="n">
         <v>129.9716</v>
       </c>
       <c r="V13" t="n">
-        <v>142.2069967833131</v>
+        <v>144.0203836074115</v>
       </c>
       <c r="W13" t="n">
-        <v>42.60516106456518</v>
+        <v>44.53470042467117</v>
       </c>
       <c r="X13" t="n">
         <v>157.9753508300781</v>
@@ -1563,11 +1575,11 @@
         <v>44.45067971191406</v>
       </c>
       <c r="Z13" t="n">
-        <v>577.0771352618034</v>
+        <v>581.4276895350062</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1576,34 +1588,34 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30.33744247004985</v>
+        <v>30.54667809968463</v>
       </c>
       <c r="D14" t="n">
-        <v>29.55478817443136</v>
+        <v>29.75862588153224</v>
       </c>
       <c r="E14" t="n">
-        <v>40.32173814677959</v>
+        <v>40.3217381467796</v>
       </c>
       <c r="F14" t="n">
-        <v>37.61617432680163</v>
+        <v>37.61617432680165</v>
       </c>
       <c r="G14" t="n">
-        <v>52.03368752641875</v>
+        <v>52.03368752641876</v>
       </c>
       <c r="H14" t="n">
-        <v>47.88945130093882</v>
+        <v>48.59085627405815</v>
       </c>
       <c r="I14" t="n">
-        <v>45.7874902800849</v>
+        <v>46.45810922677714</v>
       </c>
       <c r="J14" t="n">
-        <v>48.68369296830635</v>
+        <v>49.39673067139474</v>
       </c>
       <c r="K14" t="n">
-        <v>21.36493293502631</v>
+        <v>22.3465586998464</v>
       </c>
       <c r="L14" t="n">
-        <v>21.28927509299216</v>
+        <v>22.26742470896231</v>
       </c>
       <c r="M14" t="n">
         <v>34.5</v>
@@ -1627,16 +1639,16 @@
         <v>20.97472511873924</v>
       </c>
       <c r="T14" t="n">
-        <v>59.89223064448121</v>
+        <v>60.30530398121687</v>
       </c>
       <c r="U14" t="n">
         <v>129.9716</v>
       </c>
       <c r="V14" t="n">
-        <v>142.3606345493301</v>
+        <v>144.44569617223</v>
       </c>
       <c r="W14" t="n">
-        <v>42.65420802801847</v>
+        <v>44.61398340880871</v>
       </c>
       <c r="X14" t="n">
         <v>155.3764504150391</v>
@@ -1645,11 +1657,11 @@
         <v>42.66783985595703</v>
       </c>
       <c r="Z14" t="n">
-        <v>572.9229634928258</v>
+        <v>577.3808738332518</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1658,34 +1670,34 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30.14262515581092</v>
+        <v>30.22671295044078</v>
       </c>
       <c r="D15" t="n">
-        <v>29.36677254830259</v>
+        <v>29.448695974886</v>
       </c>
       <c r="E15" t="n">
-        <v>40.32218945504149</v>
+        <v>40.32218945504151</v>
       </c>
       <c r="F15" t="n">
-        <v>37.61024827721019</v>
+        <v>37.6102482772102</v>
       </c>
       <c r="G15" t="n">
-        <v>52.03916226774828</v>
+        <v>52.0391622677483</v>
       </c>
       <c r="H15" t="n">
-        <v>47.93082344145335</v>
+        <v>48.71580705515433</v>
       </c>
       <c r="I15" t="n">
-        <v>45.83550575471018</v>
+        <v>46.58617345369293</v>
       </c>
       <c r="J15" t="n">
-        <v>48.73114973031026</v>
+        <v>49.52924063024709</v>
       </c>
       <c r="K15" t="n">
-        <v>21.23136825654506</v>
+        <v>22.45584383421506</v>
       </c>
       <c r="L15" t="n">
-        <v>21.15983302470446</v>
+        <v>22.38018295473491</v>
       </c>
       <c r="M15" t="n">
         <v>34.5</v>
@@ -1709,16 +1721,16 @@
         <v>21.05368041161653</v>
       </c>
       <c r="T15" t="n">
-        <v>59.50939770411351</v>
+        <v>59.67540892532678</v>
       </c>
       <c r="U15" t="n">
         <v>129.9716</v>
       </c>
       <c r="V15" t="n">
-        <v>142.4974789264738</v>
+        <v>144.8312211390943</v>
       </c>
       <c r="W15" t="n">
-        <v>42.39120128124952</v>
+        <v>44.83602678894997</v>
       </c>
       <c r="X15" t="n">
         <v>156.6165752075195</v>
@@ -1727,11 +1739,11 @@
         <v>42.88806992797851</v>
       </c>
       <c r="Z15" t="n">
-        <v>573.8743230473349</v>
+        <v>578.8189019888691</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1740,34 +1752,34 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30.19973173240286</v>
+        <v>30.52484259162529</v>
       </c>
       <c r="D16" t="n">
-        <v>29.4311501156592</v>
+        <v>29.74798692026366</v>
       </c>
       <c r="E16" t="n">
-        <v>40.32304992620616</v>
+        <v>40.32304992620617</v>
       </c>
       <c r="F16" t="n">
-        <v>37.60406441961336</v>
+        <v>37.60406441961337</v>
       </c>
       <c r="G16" t="n">
-        <v>52.04448565418046</v>
+        <v>52.04448565418049</v>
       </c>
       <c r="H16" t="n">
-        <v>47.94343680401871</v>
+        <v>48.72142495169537</v>
       </c>
       <c r="I16" t="n">
-        <v>45.85280588891632</v>
+        <v>46.59686893273017</v>
       </c>
       <c r="J16" t="n">
-        <v>48.75289160159713</v>
+        <v>49.5440149410868</v>
       </c>
       <c r="K16" t="n">
-        <v>21.0877758838265</v>
+        <v>22.51426590096786</v>
       </c>
       <c r="L16" t="n">
-        <v>21.01600437953782</v>
+        <v>22.43763938802645</v>
       </c>
       <c r="M16" t="n">
         <v>34.5</v>
@@ -1791,16 +1803,16 @@
         <v>20.53777062965869</v>
       </c>
       <c r="T16" t="n">
-        <v>59.63088184806206</v>
+        <v>60.27282951188894</v>
       </c>
       <c r="U16" t="n">
         <v>129.9716</v>
       </c>
       <c r="V16" t="n">
-        <v>142.5491342945322</v>
+        <v>144.8623088255123</v>
       </c>
       <c r="W16" t="n">
-        <v>42.10378026336431</v>
+        <v>44.95190528899431</v>
       </c>
       <c r="X16" t="n">
         <v>157.3287376037597</v>
@@ -1809,11 +1821,11 @@
         <v>41.75363496398926</v>
       </c>
       <c r="Z16" t="n">
-        <v>573.3377689737076</v>
+        <v>579.1410161941446</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1822,34 +1834,34 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30.11882739163784</v>
+        <v>30.29630181741613</v>
       </c>
       <c r="D17" t="n">
-        <v>29.36427016341638</v>
+        <v>29.53729837988332</v>
       </c>
       <c r="E17" t="n">
-        <v>40.31186975272229</v>
+        <v>40.31186975272231</v>
       </c>
       <c r="F17" t="n">
-        <v>37.62126530834428</v>
+        <v>37.62126530834431</v>
       </c>
       <c r="G17" t="n">
-        <v>52.03846493893339</v>
+        <v>52.03846493893342</v>
       </c>
       <c r="H17" t="n">
-        <v>47.98999516610601</v>
+        <v>48.8525589761101</v>
       </c>
       <c r="I17" t="n">
-        <v>45.89792995046015</v>
+        <v>46.72289134485784</v>
       </c>
       <c r="J17" t="n">
-        <v>48.80077090665062</v>
+        <v>49.67790745852313</v>
       </c>
       <c r="K17" t="n">
-        <v>21.00005752280448</v>
+        <v>22.55833017592887</v>
       </c>
       <c r="L17" t="n">
-        <v>20.9292866183808</v>
+        <v>22.48230783993741</v>
       </c>
       <c r="M17" t="n">
         <v>34.5</v>
@@ -1873,16 +1885,16 @@
         <v>20.99559864303497</v>
       </c>
       <c r="T17" t="n">
-        <v>59.48309755505421</v>
+        <v>59.83360019729945</v>
       </c>
       <c r="U17" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>142.6886960232168</v>
+        <v>145.2533577794911</v>
       </c>
       <c r="W17" t="n">
-        <v>41.92934414118528</v>
+        <v>45.04063801586628</v>
       </c>
       <c r="X17" t="n">
         <v>157.8510188018799</v>
@@ -1891,11 +1903,11 @@
         <v>42.58181748199463</v>
       </c>
       <c r="Z17" t="n">
-        <v>574.5055740033308</v>
+        <v>580.5320322765315</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1904,34 +1916,34 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>30.33015759759504</v>
+        <v>30.73226351563425</v>
       </c>
       <c r="D18" t="n">
-        <v>29.54737448859139</v>
+        <v>29.93910256010414</v>
       </c>
       <c r="E18" t="n">
-        <v>40.32033576836244</v>
+        <v>40.32033576836247</v>
       </c>
       <c r="F18" t="n">
-        <v>37.61820712345775</v>
+        <v>37.61820712345777</v>
       </c>
       <c r="G18" t="n">
-        <v>52.03305710817979</v>
+        <v>52.03305710817983</v>
       </c>
       <c r="H18" t="n">
-        <v>48.04631898305853</v>
+        <v>49.00463819974535</v>
       </c>
       <c r="I18" t="n">
-        <v>45.95112177696712</v>
+        <v>46.86765074233305</v>
       </c>
       <c r="J18" t="n">
-        <v>48.85524310243023</v>
+        <v>49.82969690642454</v>
       </c>
       <c r="K18" t="n">
-        <v>20.97664945332691</v>
+        <v>22.58969384982391</v>
       </c>
       <c r="L18" t="n">
-        <v>20.9149144365044</v>
+        <v>22.5232115866323</v>
       </c>
       <c r="M18" t="n">
         <v>34.5</v>
@@ -1955,16 +1967,16 @@
         <v>21.43285489869162</v>
       </c>
       <c r="T18" t="n">
-        <v>59.87753208618643</v>
+        <v>60.67136607573839</v>
       </c>
       <c r="U18" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>142.8526838624559</v>
+        <v>145.7019858485029</v>
       </c>
       <c r="W18" t="n">
-        <v>41.8915638898313</v>
+        <v>45.1129054364562</v>
       </c>
       <c r="X18" t="n">
         <v>157.9600594009399</v>
@@ -1973,11 +1985,11 @@
         <v>43.46885874099732</v>
       </c>
       <c r="Z18" t="n">
-        <v>576.0222979804108</v>
+        <v>582.8867755026349</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1986,34 +1998,34 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30.42378537328275</v>
+        <v>30.61008662315637</v>
       </c>
       <c r="D19" t="n">
-        <v>29.62478641645079</v>
+        <v>29.80619496469379</v>
       </c>
       <c r="E19" t="n">
-        <v>40.34452776578409</v>
+        <v>40.34452776578412</v>
       </c>
       <c r="F19" t="n">
-        <v>37.61906534382382</v>
+        <v>37.61906534382386</v>
       </c>
       <c r="G19" t="n">
-        <v>52.00800689039204</v>
+        <v>52.0080068903921</v>
       </c>
       <c r="H19" t="n">
-        <v>48.093914438635</v>
+        <v>49.1511486422196</v>
       </c>
       <c r="I19" t="n">
-        <v>46.00285647233994</v>
+        <v>47.01412357115777</v>
       </c>
       <c r="J19" t="n">
-        <v>48.9136880193155</v>
+        <v>49.98894306147826</v>
       </c>
       <c r="K19" t="n">
-        <v>20.94864319140898</v>
+        <v>22.62922244255905</v>
       </c>
       <c r="L19" t="n">
-        <v>20.88038451095236</v>
+        <v>22.55548779303665</v>
       </c>
       <c r="M19" t="n">
         <v>34.5</v>
@@ -2037,16 +2049,16 @@
         <v>21.57930673093758</v>
       </c>
       <c r="T19" t="n">
-        <v>60.04857178973354</v>
+        <v>60.41628158785016</v>
       </c>
       <c r="U19" t="n">
-        <v>129.9715999999999</v>
+        <v>129.9716000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>143.0104589302904</v>
+        <v>146.1542152748556</v>
       </c>
       <c r="W19" t="n">
-        <v>41.82902770236134</v>
+        <v>45.1847102355957</v>
       </c>
       <c r="X19" t="n">
         <v>157.82792970047</v>
@@ -2055,11 +2067,11 @@
         <v>43.82067937049867</v>
       </c>
       <c r="Z19" t="n">
-        <v>576.5082674933539</v>
+        <v>583.3754161692701</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -2068,34 +2080,34 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30.23994066227622</v>
+        <v>30.28185729750932</v>
       </c>
       <c r="D20" t="n">
-        <v>29.48134406031436</v>
+        <v>29.52220917836994</v>
       </c>
       <c r="E20" t="n">
-        <v>40.26447901574749</v>
+        <v>40.26447901574753</v>
       </c>
       <c r="F20" t="n">
-        <v>37.76382507688345</v>
+        <v>37.76382507688349</v>
       </c>
       <c r="G20" t="n">
-        <v>51.94329590736901</v>
+        <v>51.94329590736907</v>
       </c>
       <c r="H20" t="n">
-        <v>48.14426233602799</v>
+        <v>49.30350049208833</v>
       </c>
       <c r="I20" t="n">
-        <v>46.05457186066899</v>
+        <v>47.16349355499845</v>
       </c>
       <c r="J20" t="n">
-        <v>48.96939980142801</v>
+        <v>50.14850597056974</v>
       </c>
       <c r="K20" t="n">
-        <v>20.84048090618955</v>
+        <v>22.53652904358072</v>
       </c>
       <c r="L20" t="n">
-        <v>20.77227909120811</v>
+        <v>22.46277680191831</v>
       </c>
       <c r="M20" t="n">
         <v>34.5</v>
@@ -2119,16 +2131,16 @@
         <v>21.63648409806365</v>
       </c>
       <c r="T20" t="n">
-        <v>59.72128472259058</v>
+        <v>59.80406647587927</v>
       </c>
       <c r="U20" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>143.168233998125</v>
+        <v>146.6155000176565</v>
       </c>
       <c r="W20" t="n">
-        <v>41.61275999739766</v>
+        <v>44.99930584549904</v>
       </c>
       <c r="X20" t="n">
         <v>157.777714850235</v>
@@ -2137,11 +2149,11 @@
         <v>43.95863968524934</v>
       </c>
       <c r="Z20" t="n">
-        <v>576.2102332535975</v>
+        <v>583.1268268745192</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2150,34 +2162,34 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.26689095984067</v>
+        <v>30.63423500985469</v>
       </c>
       <c r="D21" t="n">
-        <v>29.50547433126617</v>
+        <v>29.8635771986143</v>
       </c>
       <c r="E21" t="n">
-        <v>40.17528911957336</v>
+        <v>40.17528911957341</v>
       </c>
       <c r="F21" t="n">
-        <v>37.94690741916766</v>
+        <v>37.9469074191677</v>
       </c>
       <c r="G21" t="n">
-        <v>51.84940346125896</v>
+        <v>51.84940346125902</v>
       </c>
       <c r="H21" t="n">
-        <v>48.17891857753469</v>
+        <v>49.4375566638445</v>
       </c>
       <c r="I21" t="n">
-        <v>46.09011205710902</v>
+        <v>47.2941816408629</v>
       </c>
       <c r="J21" t="n">
-        <v>49.00863812376723</v>
+        <v>50.28895201046186</v>
       </c>
       <c r="K21" t="n">
-        <v>20.80017285448156</v>
+        <v>22.57482967008479</v>
       </c>
       <c r="L21" t="n">
-        <v>20.72779904398478</v>
+        <v>22.49628097455375</v>
       </c>
       <c r="M21" t="n">
         <v>34.5</v>
@@ -2201,16 +2213,16 @@
         <v>21.72002523987246</v>
       </c>
       <c r="T21" t="n">
-        <v>59.77236529110684</v>
+        <v>60.49781220846899</v>
       </c>
       <c r="U21" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>143.2776687584109</v>
+        <v>147.0206903151692</v>
       </c>
       <c r="W21" t="n">
-        <v>41.52797189846635</v>
+        <v>45.07111064463854</v>
       </c>
       <c r="X21" t="n">
         <v>157.7943074251175</v>
@@ -2219,11 +2231,11 @@
         <v>44.14141984262467</v>
       </c>
       <c r="Z21" t="n">
-        <v>576.4853332157263</v>
+        <v>584.4969404360191</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2232,34 +2244,34 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>30.4071300083452</v>
+        <v>30.64500183846933</v>
       </c>
       <c r="D22" t="n">
-        <v>29.60450548284728</v>
+        <v>29.83609846440103</v>
       </c>
       <c r="E22" t="n">
-        <v>40.13021174284492</v>
+        <v>40.13021174284497</v>
       </c>
       <c r="F22" t="n">
-        <v>38.04317721842566</v>
+        <v>38.04317721842571</v>
       </c>
       <c r="G22" t="n">
-        <v>51.79821103872938</v>
+        <v>51.79821103872945</v>
       </c>
       <c r="H22" t="n">
-        <v>48.21282952488362</v>
+        <v>49.56336627748452</v>
       </c>
       <c r="I22" t="n">
-        <v>46.12741390970529</v>
+        <v>47.41953404456148</v>
       </c>
       <c r="J22" t="n">
-        <v>49.0509791524921</v>
+        <v>50.42499413458957</v>
       </c>
       <c r="K22" t="n">
-        <v>20.78221339669984</v>
+        <v>22.59375788684318</v>
       </c>
       <c r="L22" t="n">
-        <v>20.70009349840719</v>
+        <v>22.50447975922992</v>
       </c>
       <c r="M22" t="n">
         <v>34.5</v>
@@ -2283,16 +2295,16 @@
         <v>21.8253597787343</v>
       </c>
       <c r="T22" t="n">
-        <v>60.01163549119248</v>
+        <v>60.48110030287035</v>
       </c>
       <c r="U22" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>143.391222587081</v>
+        <v>147.4078944566356</v>
       </c>
       <c r="W22" t="n">
-        <v>41.48230689510703</v>
+        <v>45.0982376460731</v>
       </c>
       <c r="X22" t="n">
         <v>157.7509537125588</v>
@@ -2301,11 +2313,11 @@
         <v>44.37320992131234</v>
       </c>
       <c r="Z22" t="n">
-        <v>576.9809286072515</v>
+        <v>585.0829960394502</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2314,34 +2326,34 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>30.36657185469507</v>
+        <v>30.55113515636456</v>
       </c>
       <c r="D23" t="n">
-        <v>29.57010615128269</v>
+        <v>29.74982865825887</v>
       </c>
       <c r="E23" t="n">
-        <v>40.10610650344449</v>
+        <v>40.10610650344454</v>
       </c>
       <c r="F23" t="n">
-        <v>38.09334657860402</v>
+        <v>38.09334657860407</v>
       </c>
       <c r="G23" t="n">
-        <v>51.77214691795147</v>
+        <v>51.77214691795154</v>
       </c>
       <c r="H23" t="n">
-        <v>48.21439781263772</v>
+        <v>49.69145709186481</v>
       </c>
       <c r="I23" t="n">
-        <v>46.13456318140407</v>
+        <v>47.54790624347006</v>
       </c>
       <c r="J23" t="n">
-        <v>49.0622773329853</v>
+        <v>50.56531159831638</v>
       </c>
       <c r="K23" t="n">
-        <v>20.73940063675331</v>
+        <v>22.55960116972717</v>
       </c>
       <c r="L23" t="n">
-        <v>20.76212309385253</v>
+        <v>22.58431787098256</v>
       </c>
       <c r="M23" t="n">
         <v>34.5</v>
@@ -2365,16 +2377,16 @@
         <v>21.40570173330585</v>
       </c>
       <c r="T23" t="n">
-        <v>59.93667800597777</v>
+        <v>60.30096381462343</v>
       </c>
       <c r="U23" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000002</v>
       </c>
       <c r="V23" t="n">
-        <v>143.4112383270271</v>
+        <v>147.8046749336513</v>
       </c>
       <c r="W23" t="n">
-        <v>41.50152373060584</v>
+        <v>45.14391904070973</v>
       </c>
       <c r="X23" t="n">
         <v>157.5734268562794</v>
@@ -2383,11 +2395,11 @@
         <v>43.38785496065617</v>
       </c>
       <c r="Z23" t="n">
-        <v>575.7823218805461</v>
+        <v>584.1824396059201</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2396,34 +2408,34 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>30.62294768958513</v>
+        <v>30.65410535415555</v>
       </c>
       <c r="D24" t="n">
-        <v>29.80777457130275</v>
+        <v>29.83810282876176</v>
       </c>
       <c r="E24" t="n">
-        <v>40.09481444179703</v>
+        <v>40.09481444179709</v>
       </c>
       <c r="F24" t="n">
-        <v>38.11375475444161</v>
+        <v>38.11375475444166</v>
       </c>
       <c r="G24" t="n">
-        <v>51.76303080376134</v>
+        <v>51.76303080376142</v>
       </c>
       <c r="H24" t="n">
-        <v>48.2375065811654</v>
+        <v>49.05122120630682</v>
       </c>
       <c r="I24" t="n">
-        <v>46.15852086454233</v>
+        <v>46.93716524656847</v>
       </c>
       <c r="J24" t="n">
-        <v>49.08867801779034</v>
+        <v>49.9167509855488</v>
       </c>
       <c r="K24" t="n">
-        <v>20.75586862809811</v>
+        <v>22.56779836461104</v>
       </c>
       <c r="L24" t="n">
-        <v>20.82754318215098</v>
+        <v>22.64572990834557</v>
       </c>
       <c r="M24" t="n">
         <v>34.5</v>
@@ -2447,16 +2459,16 @@
         <v>21.73236683098933</v>
       </c>
       <c r="T24" t="n">
-        <v>60.43072226088788</v>
+        <v>60.49220818291731</v>
       </c>
       <c r="U24" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000002</v>
       </c>
       <c r="V24" t="n">
-        <v>143.4847054634981</v>
+        <v>145.9051374384241</v>
       </c>
       <c r="W24" t="n">
-        <v>41.58341181024909</v>
+        <v>45.21352827295661</v>
       </c>
       <c r="X24" t="n">
         <v>157.6887634281397</v>
@@ -2465,11 +2477,11 @@
         <v>43.99642748032809</v>
       </c>
       <c r="Z24" t="n">
-        <v>577.1556304431028</v>
+        <v>583.2676648027659</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2478,34 +2490,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>30.54526099757324</v>
+        <v>30.92261420964632</v>
       </c>
       <c r="D25" t="n">
-        <v>29.7456864869155</v>
+        <v>30.11316183250342</v>
       </c>
       <c r="E25" t="n">
-        <v>40.08319709820685</v>
+        <v>40.0831970982069</v>
       </c>
       <c r="F25" t="n">
-        <v>38.12062205377768</v>
+        <v>38.12062205377774</v>
       </c>
       <c r="G25" t="n">
-        <v>51.76778084801544</v>
+        <v>51.76778084801553</v>
       </c>
       <c r="H25" t="n">
-        <v>48.25208305877177</v>
+        <v>48.75877657397292</v>
       </c>
       <c r="I25" t="n">
-        <v>46.17527021245509</v>
+        <v>46.66015518520983</v>
       </c>
       <c r="J25" t="n">
-        <v>49.10239755796093</v>
+        <v>49.61802019736375</v>
       </c>
       <c r="K25" t="n">
-        <v>20.81524530290872</v>
+        <v>22.52445121801725</v>
       </c>
       <c r="L25" t="n">
-        <v>20.91235586509793</v>
+        <v>22.62953583695659</v>
       </c>
       <c r="M25" t="n">
         <v>34.5</v>
@@ -2529,16 +2541,16 @@
         <v>21.9066926826982</v>
       </c>
       <c r="T25" t="n">
-        <v>60.29094748448874</v>
+        <v>61.03577604214973</v>
       </c>
       <c r="U25" t="n">
-        <v>129.9716</v>
+        <v>129.9716000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>143.5297508291878</v>
+        <v>145.0369519565465</v>
       </c>
       <c r="W25" t="n">
-        <v>41.72760116800666</v>
+        <v>45.15398705497384</v>
       </c>
       <c r="X25" t="n">
         <v>157.6110317140698</v>
@@ -2547,7 +2559,7 @@
         <v>44.31031374016405</v>
       </c>
       <c r="Z25" t="n">
-        <v>577.441244935917</v>
+        <v>583.1196605079042</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis Forecasting/outputs/xgboost_forecast/Day_Ahead_24H_XGBOOST.xlsx
+++ b/Thesis Forecasting/outputs/xgboost_forecast/Day_Ahead_24H_XGBOOST.xlsx
@@ -610,13 +610,13 @@
         <v>29.84301525289416</v>
       </c>
       <c r="E2" t="n">
-        <v>40.2588609705938</v>
+        <v>40.26072120167258</v>
       </c>
       <c r="F2" t="n">
-        <v>38.64860125732751</v>
+        <v>38.6503870835401</v>
       </c>
       <c r="G2" t="n">
-        <v>51.06413777207867</v>
+        <v>51.06649727986912</v>
       </c>
       <c r="H2" t="n">
         <v>47.73589529905708</v>
@@ -640,25 +640,25 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>47.41614715248679</v>
+        <v>47.35439462330712</v>
       </c>
       <c r="P2" t="n">
-        <v>28.321941349568</v>
+        <v>28.2850562035862</v>
       </c>
       <c r="Q2" t="n">
-        <v>48.08441149794521</v>
+        <v>48.02178865314585</v>
       </c>
       <c r="R2" t="n">
-        <v>21.08788786999344</v>
+        <v>21.21273535600182</v>
       </c>
       <c r="S2" t="n">
-        <v>20.84046213000656</v>
+        <v>20.96384477127556</v>
       </c>
       <c r="T2" t="n">
         <v>60.75735086107552</v>
       </c>
       <c r="U2" t="n">
-        <v>129.9716</v>
+        <v>129.9776055650818</v>
       </c>
       <c r="V2" t="n">
         <v>141.3063620286986</v>
@@ -667,13 +667,13 @@
         <v>43.65485927581787</v>
       </c>
       <c r="X2" t="n">
-        <v>158.3225</v>
+        <v>158.1612394800392</v>
       </c>
       <c r="Y2" t="n">
-        <v>41.92835</v>
+        <v>42.17658012727738</v>
       </c>
       <c r="Z2" t="n">
-        <v>575.941022165592</v>
+        <v>576.0339973379904</v>
       </c>
     </row>
     <row r="3">
@@ -692,13 +692,13 @@
         <v>29.83828005388596</v>
       </c>
       <c r="E3" t="n">
-        <v>40.33240941262922</v>
+        <v>40.33823368667311</v>
       </c>
       <c r="F3" t="n">
-        <v>38.12644566342365</v>
+        <v>38.13195138130902</v>
       </c>
       <c r="G3" t="n">
-        <v>51.51274492394714</v>
+        <v>51.52018371442753</v>
       </c>
       <c r="H3" t="n">
         <v>47.81157837152412</v>
@@ -722,25 +722,25 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>44.87902252362228</v>
+        <v>45.07052986748023</v>
       </c>
       <c r="P3" t="n">
-        <v>26.66202747637768</v>
+        <v>26.77576463080414</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
       </c>
       <c r="R3" t="n">
-        <v>21.22653310157816</v>
+        <v>21.22584834429197</v>
       </c>
       <c r="S3" t="n">
-        <v>20.91599189842184</v>
+        <v>20.91531715903874</v>
       </c>
       <c r="T3" t="n">
         <v>60.6246789531976</v>
       </c>
       <c r="U3" t="n">
-        <v>129.9716</v>
+        <v>129.9903687824097</v>
       </c>
       <c r="V3" t="n">
         <v>141.8565027011722</v>
@@ -749,13 +749,13 @@
         <v>43.10187402486801</v>
       </c>
       <c r="X3" t="n">
-        <v>156.04105</v>
+        <v>156.3462944982844</v>
       </c>
       <c r="Y3" t="n">
-        <v>42.14252500000001</v>
+        <v>42.14116550333071</v>
       </c>
       <c r="Z3" t="n">
-        <v>573.7382306792377</v>
+        <v>574.0608844632626</v>
       </c>
     </row>
     <row r="4">
@@ -774,13 +774,13 @@
         <v>30.0741735420212</v>
       </c>
       <c r="E4" t="n">
-        <v>40.47405329288873</v>
+        <v>40.47546559423805</v>
       </c>
       <c r="F4" t="n">
-        <v>37.8199506328184</v>
+        <v>37.82127032192697</v>
       </c>
       <c r="G4" t="n">
-        <v>51.67759607429286</v>
+        <v>51.6793993119903</v>
       </c>
       <c r="H4" t="n">
         <v>47.90717935496485</v>
@@ -804,25 +804,25 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>46.91721250332506</v>
+        <v>46.84574509289578</v>
       </c>
       <c r="P4" t="n">
-        <v>26.11041249667492</v>
+        <v>26.07398750585292</v>
       </c>
       <c r="Q4" t="n">
         <v>50</v>
       </c>
       <c r="R4" t="n">
-        <v>22.27519794513418</v>
+        <v>22.08320418740758</v>
       </c>
       <c r="S4" t="n">
-        <v>21.90691455486583</v>
+        <v>21.71809509494705</v>
       </c>
       <c r="T4" t="n">
         <v>61.07703749869168</v>
       </c>
       <c r="U4" t="n">
-        <v>129.9716</v>
+        <v>129.9761352281553</v>
       </c>
       <c r="V4" t="n">
         <v>142.307182101287</v>
@@ -831,13 +831,13 @@
         <v>43.63820126771927</v>
       </c>
       <c r="X4" t="n">
-        <v>157.527625</v>
+        <v>157.4197325987487</v>
       </c>
       <c r="Y4" t="n">
-        <v>44.1821125</v>
+        <v>43.80129928235463</v>
       </c>
       <c r="Z4" t="n">
-        <v>578.703758367698</v>
+        <v>578.2195879769566</v>
       </c>
     </row>
     <row r="5">
@@ -856,13 +856,13 @@
         <v>30.20323563289052</v>
       </c>
       <c r="E5" t="n">
-        <v>40.53966881175825</v>
+        <v>40.54386296884601</v>
       </c>
       <c r="F5" t="n">
-        <v>37.68909958966155</v>
+        <v>37.69299883227524</v>
       </c>
       <c r="G5" t="n">
-        <v>51.7428315985802</v>
+        <v>51.74818481359777</v>
       </c>
       <c r="H5" t="n">
         <v>48.061087940654</v>
@@ -886,25 +886,25 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>47.61289949852959</v>
+        <v>47.57291407582738</v>
       </c>
       <c r="P5" t="n">
-        <v>25.75461300147043</v>
+        <v>25.73530430526921</v>
       </c>
       <c r="Q5" t="n">
         <v>50</v>
       </c>
       <c r="R5" t="n">
-        <v>22.88091126156748</v>
+        <v>22.64473362533801</v>
       </c>
       <c r="S5" t="n">
-        <v>22.49639498843253</v>
+        <v>22.26418634379796</v>
       </c>
       <c r="T5" t="n">
         <v>61.31931191981137</v>
       </c>
       <c r="U5" t="n">
-        <v>129.9716</v>
+        <v>129.985046614719</v>
       </c>
       <c r="V5" t="n">
         <v>142.8511050779879</v>
@@ -913,13 +913,13 @@
         <v>44.18283364295959</v>
       </c>
       <c r="X5" t="n">
-        <v>157.8675125</v>
+        <v>157.8082183810966</v>
       </c>
       <c r="Y5" t="n">
-        <v>45.37730625</v>
+        <v>44.90891996913597</v>
       </c>
       <c r="Z5" t="n">
-        <v>581.5696693907589</v>
+        <v>581.0554356057104</v>
       </c>
     </row>
     <row r="6">
@@ -938,13 +938,13 @@
         <v>30.23584682395321</v>
       </c>
       <c r="E6" t="n">
-        <v>40.57726522972613</v>
+        <v>40.58257939106128</v>
       </c>
       <c r="F6" t="n">
-        <v>37.60768300104473</v>
+        <v>37.61260825398568</v>
       </c>
       <c r="G6" t="n">
-        <v>51.78665176922914</v>
+        <v>51.7934339567657</v>
       </c>
       <c r="H6" t="n">
         <v>48.18118984002477</v>
@@ -968,25 +968,25 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>48.31246961784986</v>
+        <v>48.28682814834086</v>
       </c>
       <c r="P6" t="n">
-        <v>25.01253663215013</v>
+        <v>25.00077977730972</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
       </c>
       <c r="R6" t="n">
-        <v>23.23642350707111</v>
+        <v>22.957648184753</v>
       </c>
       <c r="S6" t="n">
-        <v>22.83347961792889</v>
+        <v>22.55953855130153</v>
       </c>
       <c r="T6" t="n">
         <v>61.41040276315509</v>
       </c>
       <c r="U6" t="n">
-        <v>129.9716</v>
+        <v>129.9886216018127</v>
       </c>
       <c r="V6" t="n">
         <v>143.2458747252569</v>
@@ -995,13 +995,13 @@
         <v>44.37952399373054</v>
       </c>
       <c r="X6" t="n">
-        <v>157.82500625</v>
+        <v>157.7876079256506</v>
       </c>
       <c r="Y6" t="n">
-        <v>46.069903125</v>
+        <v>45.51718673605454</v>
       </c>
       <c r="Z6" t="n">
-        <v>582.9023108571425</v>
+        <v>582.3292177456605</v>
       </c>
     </row>
     <row r="7">
@@ -1020,13 +1020,13 @@
         <v>30.18092087355631</v>
       </c>
       <c r="E7" t="n">
-        <v>40.48299959464393</v>
+        <v>40.48274066159035</v>
       </c>
       <c r="F7" t="n">
-        <v>37.62379444748178</v>
+        <v>37.62355380217186</v>
       </c>
       <c r="G7" t="n">
-        <v>51.86480595787428</v>
+        <v>51.86447422572216</v>
       </c>
       <c r="H7" t="n">
         <v>48.28393417591501</v>
@@ -1050,25 +1050,25 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>48.70607997557301</v>
+        <v>48.65958491374335</v>
       </c>
       <c r="P7" t="n">
-        <v>24.29267314942699</v>
+        <v>24.27052813482783</v>
       </c>
       <c r="Q7" t="n">
         <v>50</v>
       </c>
       <c r="R7" t="n">
-        <v>22.70354257149103</v>
+        <v>22.46543510199804</v>
       </c>
       <c r="S7" t="n">
-        <v>22.30765899100898</v>
+        <v>22.07370342147899</v>
       </c>
       <c r="T7" t="n">
         <v>61.23515631149111</v>
       </c>
       <c r="U7" t="n">
-        <v>129.9716</v>
+        <v>129.9707686894844</v>
       </c>
       <c r="V7" t="n">
         <v>143.5805431428284</v>
@@ -1077,13 +1077,13 @@
         <v>44.42490470528602</v>
       </c>
       <c r="X7" t="n">
-        <v>157.498753125</v>
+        <v>157.4301130485712</v>
       </c>
       <c r="Y7" t="n">
-        <v>45.01120156250001</v>
+        <v>44.53913852347703</v>
       </c>
       <c r="Z7" t="n">
-        <v>581.7221588471054</v>
+        <v>581.1806244211382</v>
       </c>
     </row>
     <row r="8">
@@ -1102,13 +1102,13 @@
         <v>29.98136707009827</v>
       </c>
       <c r="E8" t="n">
-        <v>40.39242388841581</v>
+        <v>40.38793234216693</v>
       </c>
       <c r="F8" t="n">
-        <v>37.63550649093683</v>
+        <v>37.63132150767188</v>
       </c>
       <c r="G8" t="n">
-        <v>51.94366962064734</v>
+        <v>51.93789360197902</v>
       </c>
       <c r="H8" t="n">
         <v>47.98227189432207</v>
@@ -1132,25 +1132,25 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>49.37897687737681</v>
+        <v>49.24141820188375</v>
       </c>
       <c r="P8" t="n">
-        <v>23.81494968512318</v>
+        <v>23.74913096285704</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
       </c>
       <c r="R8" t="n">
-        <v>20.47483450017041</v>
+        <v>20.55650536409107</v>
       </c>
       <c r="S8" t="n">
-        <v>20.11161628107959</v>
+        <v>20.19183832519442</v>
       </c>
       <c r="T8" t="n">
         <v>60.83053172073659</v>
       </c>
       <c r="U8" t="n">
-        <v>129.9716</v>
+        <v>129.9571474518178</v>
       </c>
       <c r="V8" t="n">
         <v>142.706584742488</v>
@@ -1159,13 +1159,13 @@
         <v>42.88016784310341</v>
       </c>
       <c r="X8" t="n">
-        <v>157.6939265625</v>
+        <v>157.4905491647408</v>
       </c>
       <c r="Y8" t="n">
-        <v>40.58645078125</v>
+        <v>40.7483436892855</v>
       </c>
       <c r="Z8" t="n">
-        <v>574.6692616500781</v>
+        <v>574.6133246121722</v>
       </c>
     </row>
     <row r="9">
@@ -1184,13 +1184,13 @@
         <v>29.93844046965392</v>
       </c>
       <c r="E9" t="n">
-        <v>40.32825151309163</v>
+        <v>40.3176768119221</v>
       </c>
       <c r="F9" t="n">
-        <v>37.65644011242598</v>
+        <v>37.64656600218424</v>
       </c>
       <c r="G9" t="n">
-        <v>51.98690837448238</v>
+        <v>51.97327659030721</v>
       </c>
       <c r="H9" t="n">
         <v>47.6909601219564</v>
@@ -1217,22 +1217,22 @@
         <v>50</v>
       </c>
       <c r="P9" t="n">
-        <v>23.85657506408953</v>
+        <v>23.75421938025831</v>
       </c>
       <c r="Q9" t="n">
-        <v>49.67493821716049</v>
+        <v>49.57784441418792</v>
       </c>
       <c r="R9" t="n">
-        <v>20.15874339502009</v>
+        <v>20.17971442448512</v>
       </c>
       <c r="S9" t="n">
-        <v>19.82533199560491</v>
+        <v>19.84595617903177</v>
       </c>
       <c r="T9" t="n">
         <v>60.74790658283529</v>
       </c>
       <c r="U9" t="n">
-        <v>129.9716</v>
+        <v>129.9375194044136</v>
       </c>
       <c r="V9" t="n">
         <v>141.8552357548178</v>
@@ -1241,13 +1241,13 @@
         <v>44.08900070309639</v>
       </c>
       <c r="X9" t="n">
-        <v>158.03151328125</v>
+        <v>157.8320637944462</v>
       </c>
       <c r="Y9" t="n">
-        <v>39.98407539062501</v>
+        <v>40.02567060351689</v>
       </c>
       <c r="Z9" t="n">
-        <v>574.6793317126245</v>
+        <v>574.4873968431262</v>
       </c>
     </row>
     <row r="10">
@@ -1266,13 +1266,13 @@
         <v>29.85828226017761</v>
       </c>
       <c r="E10" t="n">
-        <v>40.31090614286469</v>
+        <v>40.30470242790046</v>
       </c>
       <c r="F10" t="n">
-        <v>37.64147643066631</v>
+        <v>37.63568353209487</v>
       </c>
       <c r="G10" t="n">
-        <v>52.01921742646901</v>
+        <v>52.01121184117077</v>
       </c>
       <c r="H10" t="n">
         <v>47.87253253455204</v>
@@ -1296,25 +1296,25 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>48.12695120493856</v>
+        <v>48.10380935974281</v>
       </c>
       <c r="P10" t="n">
-        <v>25.18005543568642</v>
+        <v>25.07616388900221</v>
       </c>
       <c r="Q10" t="n">
         <v>50</v>
       </c>
       <c r="R10" t="n">
-        <v>21.55728001234058</v>
+        <v>21.3602791087961</v>
       </c>
       <c r="S10" t="n">
-        <v>21.07555768297193</v>
+        <v>20.88295899223392</v>
       </c>
       <c r="T10" t="n">
         <v>60.56046039877234</v>
       </c>
       <c r="U10" t="n">
-        <v>129.9716</v>
+        <v>129.9515978011661</v>
       </c>
       <c r="V10" t="n">
         <v>142.3789612058983</v>
@@ -1323,13 +1323,13 @@
         <v>43.93536825597286</v>
       </c>
       <c r="X10" t="n">
-        <v>157.807006640625</v>
+        <v>157.679973248745</v>
       </c>
       <c r="Y10" t="n">
-        <v>42.6328376953125</v>
+        <v>42.24323810103002</v>
       </c>
       <c r="Z10" t="n">
-        <v>577.2862341965811</v>
+        <v>576.7495990115846</v>
       </c>
     </row>
     <row r="11">
@@ -1348,13 +1348,13 @@
         <v>29.68349777298189</v>
       </c>
       <c r="E11" t="n">
-        <v>40.30634245574819</v>
+        <v>40.29696068791671</v>
       </c>
       <c r="F11" t="n">
-        <v>37.62763226357113</v>
+        <v>37.6188739965482</v>
       </c>
       <c r="G11" t="n">
-        <v>52.03762528068068</v>
+        <v>52.0255129209591</v>
       </c>
       <c r="H11" t="n">
         <v>48.06517429399553</v>
@@ -1378,25 +1378,25 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>48.03411818653069</v>
+        <v>47.99548009021208</v>
       </c>
       <c r="P11" t="n">
-        <v>25.1314851337818</v>
+        <v>25.019692633339</v>
       </c>
       <c r="Q11" t="n">
         <v>50</v>
       </c>
       <c r="R11" t="n">
-        <v>22.18457939246321</v>
+        <v>22.04106427595969</v>
       </c>
       <c r="S11" t="n">
-        <v>21.68893945519304</v>
+        <v>21.54863070208649</v>
       </c>
       <c r="T11" t="n">
         <v>60.17828353512881</v>
       </c>
       <c r="U11" t="n">
-        <v>129.9716</v>
+        <v>129.941347605424</v>
       </c>
       <c r="V11" t="n">
         <v>142.9283938198955</v>
@@ -1405,13 +1405,13 @@
         <v>44.24413494884968</v>
       </c>
       <c r="X11" t="n">
-        <v>157.6656033203125</v>
+        <v>157.5151727235511</v>
       </c>
       <c r="Y11" t="n">
-        <v>43.87351884765625</v>
+        <v>43.58969497804618</v>
       </c>
       <c r="Z11" t="n">
-        <v>578.8615344718427</v>
+        <v>578.3970276108952</v>
       </c>
     </row>
     <row r="12">
@@ -1430,13 +1430,13 @@
         <v>29.92949144837918</v>
       </c>
       <c r="E12" t="n">
-        <v>40.30594173893525</v>
+        <v>40.2954083769519</v>
       </c>
       <c r="F12" t="n">
-        <v>37.62563604402251</v>
+        <v>37.61580314030641</v>
       </c>
       <c r="G12" t="n">
-        <v>52.04002221704224</v>
+        <v>52.02642232660465</v>
       </c>
       <c r="H12" t="n">
         <v>48.25964217113603</v>
@@ -1460,25 +1460,25 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>48.07521476631519</v>
+        <v>47.97407712923132</v>
       </c>
       <c r="P12" t="n">
-        <v>25.15298689384103</v>
+        <v>25.00853542636502</v>
       </c>
       <c r="Q12" t="n">
         <v>50</v>
       </c>
       <c r="R12" t="n">
-        <v>22.5241111200988</v>
+        <v>22.29541151196223</v>
       </c>
       <c r="S12" t="n">
-        <v>21.88724830372933</v>
+        <v>21.66501511177068</v>
       </c>
       <c r="T12" t="n">
         <v>60.66858031352972</v>
       </c>
       <c r="U12" t="n">
-        <v>129.9716</v>
+        <v>129.937633843863</v>
       </c>
       <c r="V12" t="n">
         <v>143.4949385250763</v>
@@ -1487,13 +1487,13 @@
         <v>44.32992777347565</v>
       </c>
       <c r="X12" t="n">
-        <v>157.7282016601562</v>
+        <v>157.4826125555963</v>
       </c>
       <c r="Y12" t="n">
-        <v>44.41135942382813</v>
+        <v>43.9604266237329</v>
       </c>
       <c r="Z12" t="n">
-        <v>580.6046076960661</v>
+        <v>579.8741196352739</v>
       </c>
     </row>
     <row r="13">
@@ -1512,13 +1512,13 @@
         <v>29.8475352192162</v>
       </c>
       <c r="E13" t="n">
-        <v>40.31065176990718</v>
+        <v>40.29044062758208</v>
       </c>
       <c r="F13" t="n">
-        <v>37.63130939843649</v>
+        <v>37.61244163726823</v>
       </c>
       <c r="G13" t="n">
-        <v>52.02963883165631</v>
+        <v>52.0035519690188</v>
       </c>
       <c r="H13" t="n">
         <v>48.44143227564274</v>
@@ -1542,25 +1542,25 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>48.2374712351884</v>
+        <v>48.10287013739656</v>
       </c>
       <c r="P13" t="n">
-        <v>25.23787959488973</v>
+        <v>25.07567427926452</v>
       </c>
       <c r="Q13" t="n">
         <v>50</v>
       </c>
       <c r="R13" t="n">
-        <v>22.58996573902358</v>
+        <v>22.32300947896475</v>
       </c>
       <c r="S13" t="n">
-        <v>21.86071397289049</v>
+        <v>21.60237562426975</v>
       </c>
       <c r="T13" t="n">
         <v>60.47497496093128</v>
       </c>
       <c r="U13" t="n">
-        <v>129.9716</v>
+        <v>129.9064342338691</v>
       </c>
       <c r="V13" t="n">
         <v>144.0203836074115</v>
@@ -1569,13 +1569,13 @@
         <v>44.53470042467117</v>
       </c>
       <c r="X13" t="n">
-        <v>157.9753508300781</v>
+        <v>157.6785444166611</v>
       </c>
       <c r="Y13" t="n">
-        <v>44.45067971191406</v>
+        <v>43.9253851032345</v>
       </c>
       <c r="Z13" t="n">
-        <v>581.4276895350062</v>
+        <v>580.5404227467786</v>
       </c>
     </row>
     <row r="14">
@@ -1594,13 +1594,13 @@
         <v>29.75862588153224</v>
       </c>
       <c r="E14" t="n">
-        <v>40.3217381467796</v>
+        <v>40.30082327027366</v>
       </c>
       <c r="F14" t="n">
-        <v>37.61617432680165</v>
+        <v>37.59666282564049</v>
       </c>
       <c r="G14" t="n">
-        <v>52.03368752641876</v>
+        <v>52.00669766440432</v>
       </c>
       <c r="H14" t="n">
         <v>48.59085627405815</v>
@@ -1624,25 +1624,25 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>46.53126115796824</v>
+        <v>46.66992153273191</v>
       </c>
       <c r="P14" t="n">
-        <v>24.34518925707083</v>
+        <v>24.32868865518711</v>
       </c>
       <c r="Q14" t="n">
         <v>50</v>
       </c>
       <c r="R14" t="n">
-        <v>21.69311473721778</v>
+        <v>21.56283047941255</v>
       </c>
       <c r="S14" t="n">
-        <v>20.97472511873924</v>
+        <v>20.84875535700302</v>
       </c>
       <c r="T14" t="n">
         <v>60.30530398121687</v>
       </c>
       <c r="U14" t="n">
-        <v>129.9716</v>
+        <v>129.9041837603185</v>
       </c>
       <c r="V14" t="n">
         <v>144.44569617223</v>
@@ -1651,13 +1651,13 @@
         <v>44.61398340880871</v>
       </c>
       <c r="X14" t="n">
-        <v>155.3764504150391</v>
+        <v>155.498610187919</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.66783985595703</v>
+        <v>42.41158583641557</v>
       </c>
       <c r="Z14" t="n">
-        <v>577.3808738332518</v>
+        <v>577.1793633469086</v>
       </c>
     </row>
     <row r="15">
@@ -1676,13 +1676,13 @@
         <v>29.448695974886</v>
       </c>
       <c r="E15" t="n">
-        <v>40.32218945504151</v>
+        <v>40.29817742711174</v>
       </c>
       <c r="F15" t="n">
-        <v>37.6102482772102</v>
+        <v>37.5878512212893</v>
       </c>
       <c r="G15" t="n">
-        <v>52.0391622677483</v>
+        <v>52.00817273482107</v>
       </c>
       <c r="H15" t="n">
         <v>48.71580705515433</v>
@@ -1706,25 +1706,25 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>47.34541833217028</v>
+        <v>47.21627502604056</v>
       </c>
       <c r="P15" t="n">
-        <v>24.77115687534924</v>
+        <v>24.61349873409539</v>
       </c>
       <c r="Q15" t="n">
         <v>50</v>
       </c>
       <c r="R15" t="n">
-        <v>21.83438951636198</v>
+        <v>21.63452887368783</v>
       </c>
       <c r="S15" t="n">
-        <v>21.05368041161653</v>
+        <v>20.86096597393698</v>
       </c>
       <c r="T15" t="n">
         <v>59.67540892532678</v>
       </c>
       <c r="U15" t="n">
-        <v>129.9716</v>
+        <v>129.8942013832221</v>
       </c>
       <c r="V15" t="n">
         <v>144.8312211390943</v>
@@ -1733,13 +1733,13 @@
         <v>44.83602678894997</v>
       </c>
       <c r="X15" t="n">
-        <v>156.6165752075195</v>
+        <v>156.3297737601359</v>
       </c>
       <c r="Y15" t="n">
-        <v>42.88806992797851</v>
+        <v>42.49549484762482</v>
       </c>
       <c r="Z15" t="n">
-        <v>578.8189019888691</v>
+        <v>578.062126844354</v>
       </c>
     </row>
     <row r="16">
@@ -1758,13 +1758,13 @@
         <v>29.74798692026366</v>
       </c>
       <c r="E16" t="n">
-        <v>40.32304992620617</v>
+        <v>40.29534140019768</v>
       </c>
       <c r="F16" t="n">
-        <v>37.60406441961337</v>
+        <v>37.5782242810598</v>
       </c>
       <c r="G16" t="n">
-        <v>52.04448565418049</v>
+        <v>52.00872258598532</v>
       </c>
       <c r="H16" t="n">
         <v>48.72142495169537</v>
@@ -1788,25 +1788,25 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>47.81296170168567</v>
+        <v>47.66255756067572</v>
       </c>
       <c r="P16" t="n">
-        <v>25.01577590207406</v>
+        <v>24.84614255437204</v>
       </c>
       <c r="Q16" t="n">
         <v>50</v>
       </c>
       <c r="R16" t="n">
-        <v>21.21586433433057</v>
+        <v>21.11277799938667</v>
       </c>
       <c r="S16" t="n">
-        <v>20.53777062965869</v>
+        <v>20.43797910248984</v>
       </c>
       <c r="T16" t="n">
         <v>60.27282951188894</v>
       </c>
       <c r="U16" t="n">
-        <v>129.9716</v>
+        <v>129.8822882672428</v>
       </c>
       <c r="V16" t="n">
         <v>144.8623088255123</v>
@@ -1815,13 +1815,13 @@
         <v>44.95190528899431</v>
       </c>
       <c r="X16" t="n">
-        <v>157.3287376037597</v>
+        <v>157.0087001150478</v>
       </c>
       <c r="Y16" t="n">
-        <v>41.75363496398926</v>
+        <v>41.5507571018765</v>
       </c>
       <c r="Z16" t="n">
-        <v>579.1410161941446</v>
+        <v>578.5287891105627</v>
       </c>
     </row>
     <row r="17">
@@ -1840,13 +1840,13 @@
         <v>29.53729837988332</v>
       </c>
       <c r="E17" t="n">
-        <v>40.31186975272231</v>
+        <v>40.28248618562312</v>
       </c>
       <c r="F17" t="n">
-        <v>37.62126530834431</v>
+        <v>37.59384293919286</v>
       </c>
       <c r="G17" t="n">
-        <v>52.03846493893342</v>
+        <v>52.0005337852645</v>
       </c>
       <c r="H17" t="n">
         <v>48.8525589761101</v>
@@ -1870,25 +1870,25 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>47.03471229194007</v>
+        <v>46.84065329994889</v>
       </c>
       <c r="P17" t="n">
-        <v>26.31630650993981</v>
+        <v>26.12025156643419</v>
       </c>
       <c r="Q17" t="n">
         <v>50</v>
       </c>
       <c r="R17" t="n">
-        <v>21.58621883895966</v>
+        <v>21.34630329998995</v>
       </c>
       <c r="S17" t="n">
-        <v>20.99559864303497</v>
+        <v>20.76224742937341</v>
       </c>
       <c r="T17" t="n">
         <v>59.83360019729945</v>
       </c>
       <c r="U17" t="n">
-        <v>129.9716000000001</v>
+        <v>129.8768629100805</v>
       </c>
       <c r="V17" t="n">
         <v>145.2533577794911</v>
@@ -1897,13 +1897,13 @@
         <v>45.04063801586628</v>
       </c>
       <c r="X17" t="n">
-        <v>157.8510188018799</v>
+        <v>157.4609048663831</v>
       </c>
       <c r="Y17" t="n">
-        <v>42.58181748199463</v>
+        <v>42.10855072936336</v>
       </c>
       <c r="Z17" t="n">
-        <v>580.5320322765315</v>
+        <v>579.5739144984838</v>
       </c>
     </row>
     <row r="18">
@@ -1922,13 +1922,13 @@
         <v>29.93910256010414</v>
       </c>
       <c r="E18" t="n">
-        <v>40.32033576836247</v>
+        <v>40.28915269579897</v>
       </c>
       <c r="F18" t="n">
-        <v>37.61820712345777</v>
+        <v>37.58911383194407</v>
       </c>
       <c r="G18" t="n">
-        <v>52.03305710817983</v>
+        <v>51.99281561304878</v>
       </c>
       <c r="H18" t="n">
         <v>49.00463819974535</v>
@@ -1952,25 +1952,25 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>43.61213266161683</v>
+        <v>43.42113995343808</v>
       </c>
       <c r="P18" t="n">
-        <v>29.8479267393231</v>
+        <v>29.64512991559693</v>
       </c>
       <c r="Q18" t="n">
         <v>50</v>
       </c>
       <c r="R18" t="n">
-        <v>22.0360038423057</v>
+        <v>21.71253733776346</v>
       </c>
       <c r="S18" t="n">
-        <v>21.43285489869162</v>
+        <v>21.11824201760603</v>
       </c>
       <c r="T18" t="n">
         <v>60.67136607573839</v>
       </c>
       <c r="U18" t="n">
-        <v>129.9716000000001</v>
+        <v>129.8710821407918</v>
       </c>
       <c r="V18" t="n">
         <v>145.7019858485029</v>
@@ -1979,13 +1979,13 @@
         <v>45.1129054364562</v>
       </c>
       <c r="X18" t="n">
-        <v>157.9600594009399</v>
+        <v>157.566269869035</v>
       </c>
       <c r="Y18" t="n">
-        <v>43.46885874099732</v>
+        <v>42.83077935536949</v>
       </c>
       <c r="Z18" t="n">
-        <v>582.8867755026349</v>
+        <v>581.7543887258939</v>
       </c>
     </row>
     <row r="19">
@@ -2004,13 +2004,13 @@
         <v>29.80619496469379</v>
       </c>
       <c r="E19" t="n">
-        <v>40.34452776578412</v>
+        <v>40.31333983853417</v>
       </c>
       <c r="F19" t="n">
-        <v>37.61906534382386</v>
+        <v>37.58998430760587</v>
       </c>
       <c r="G19" t="n">
-        <v>52.0080068903921</v>
+        <v>51.96780262911709</v>
       </c>
       <c r="H19" t="n">
         <v>49.1511486422196</v>
@@ -2034,25 +2034,25 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>42.32695983160359</v>
+        <v>42.16596337548351</v>
       </c>
       <c r="P19" t="n">
-        <v>31.00096986886637</v>
+        <v>30.82344894748133</v>
       </c>
       <c r="Q19" t="n">
         <v>50</v>
       </c>
       <c r="R19" t="n">
-        <v>22.24137263956109</v>
+        <v>21.9196959826831</v>
       </c>
       <c r="S19" t="n">
-        <v>21.57930673093758</v>
+        <v>21.26720552390121</v>
       </c>
       <c r="T19" t="n">
         <v>60.41628158785016</v>
       </c>
       <c r="U19" t="n">
-        <v>129.9716000000001</v>
+        <v>129.8711267752572</v>
       </c>
       <c r="V19" t="n">
         <v>146.1542152748556</v>
@@ -2061,13 +2061,13 @@
         <v>45.1847102355957</v>
       </c>
       <c r="X19" t="n">
-        <v>157.82792970047</v>
+        <v>157.4894123229648</v>
       </c>
       <c r="Y19" t="n">
-        <v>43.82067937049867</v>
+        <v>43.18690150658431</v>
       </c>
       <c r="Z19" t="n">
-        <v>583.3754161692701</v>
+        <v>582.3026477031078</v>
       </c>
     </row>
     <row r="20">
@@ -2086,13 +2086,13 @@
         <v>29.52220917836994</v>
       </c>
       <c r="E20" t="n">
-        <v>40.26447901574753</v>
+        <v>40.22504306619977</v>
       </c>
       <c r="F20" t="n">
-        <v>37.76382507688349</v>
+        <v>37.72683832486616</v>
       </c>
       <c r="G20" t="n">
-        <v>51.94329590736907</v>
+        <v>51.8924214580574</v>
       </c>
       <c r="H20" t="n">
         <v>49.30350049208833</v>
@@ -2116,25 +2116,25 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>42.84830177117978</v>
+        <v>42.67482011981683</v>
       </c>
       <c r="P20" t="n">
-        <v>30.42941307905521</v>
+        <v>30.2548875294323</v>
       </c>
       <c r="Q20" t="n">
         <v>50</v>
       </c>
       <c r="R20" t="n">
-        <v>22.32215558718569</v>
+        <v>21.93173816137949</v>
       </c>
       <c r="S20" t="n">
-        <v>21.63648409806365</v>
+        <v>21.25805915643695</v>
       </c>
       <c r="T20" t="n">
         <v>59.80406647587927</v>
       </c>
       <c r="U20" t="n">
-        <v>129.9716000000001</v>
+        <v>129.8443028491233</v>
       </c>
       <c r="V20" t="n">
         <v>146.6155000176565</v>
@@ -2143,13 +2143,13 @@
         <v>44.99930584549904</v>
       </c>
       <c r="X20" t="n">
-        <v>157.777714850235</v>
+        <v>157.4297076492491</v>
       </c>
       <c r="Y20" t="n">
-        <v>43.95863968524934</v>
+        <v>43.18979731781644</v>
       </c>
       <c r="Z20" t="n">
-        <v>583.1268268745192</v>
+        <v>581.8826801552237</v>
       </c>
     </row>
     <row r="21">
@@ -2168,13 +2168,13 @@
         <v>29.8635771986143</v>
       </c>
       <c r="E21" t="n">
-        <v>40.17528911957341</v>
+        <v>40.13428998058632</v>
       </c>
       <c r="F21" t="n">
-        <v>37.9469074191677</v>
+        <v>37.90818235792973</v>
       </c>
       <c r="G21" t="n">
-        <v>51.84940346125902</v>
+        <v>51.79649081406986</v>
       </c>
       <c r="H21" t="n">
         <v>49.4375566638445</v>
@@ -2198,25 +2198,25 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>43.31719562114957</v>
+        <v>43.08990517626809</v>
       </c>
       <c r="P21" t="n">
-        <v>29.97711180396793</v>
+        <v>29.77555796733811</v>
       </c>
       <c r="Q21" t="n">
         <v>50</v>
       </c>
       <c r="R21" t="n">
-        <v>22.42139460275222</v>
+        <v>22.01198643217835</v>
       </c>
       <c r="S21" t="n">
-        <v>21.72002523987246</v>
+        <v>21.32342387069702</v>
       </c>
       <c r="T21" t="n">
         <v>60.49781220846899</v>
       </c>
       <c r="U21" t="n">
-        <v>129.9716000000001</v>
+        <v>129.8389631525859</v>
       </c>
       <c r="V21" t="n">
         <v>147.0206903151692</v>
@@ -2225,13 +2225,13 @@
         <v>45.07111064463854</v>
       </c>
       <c r="X21" t="n">
-        <v>157.7943074251175</v>
+        <v>157.3654631436062</v>
       </c>
       <c r="Y21" t="n">
-        <v>44.14141984262467</v>
+        <v>43.33541030287537</v>
       </c>
       <c r="Z21" t="n">
-        <v>584.4969404360191</v>
+        <v>583.1294497673442</v>
       </c>
     </row>
     <row r="22">
@@ -2250,13 +2250,13 @@
         <v>29.83609846440103</v>
       </c>
       <c r="E22" t="n">
-        <v>40.13021174284497</v>
+        <v>40.08712447950862</v>
       </c>
       <c r="F22" t="n">
-        <v>38.04317721842571</v>
+        <v>38.00233077571403</v>
       </c>
       <c r="G22" t="n">
-        <v>51.79821103872945</v>
+        <v>51.74259600301323</v>
       </c>
       <c r="H22" t="n">
         <v>49.56336627748452</v>
@@ -2280,25 +2280,25 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>43.6784184084262</v>
+        <v>43.44897042219421</v>
       </c>
       <c r="P22" t="n">
-        <v>29.57253530413255</v>
+        <v>29.3786585840002</v>
       </c>
       <c r="Q22" t="n">
         <v>50</v>
       </c>
       <c r="R22" t="n">
-        <v>22.54785014257804</v>
+        <v>22.12436698425874</v>
       </c>
       <c r="S22" t="n">
-        <v>21.8253597787343</v>
+        <v>21.41544609596149</v>
       </c>
       <c r="T22" t="n">
         <v>60.48110030287035</v>
       </c>
       <c r="U22" t="n">
-        <v>129.9716000000001</v>
+        <v>129.8320512582359</v>
       </c>
       <c r="V22" t="n">
         <v>147.4078944566356</v>
@@ -2307,13 +2307,13 @@
         <v>45.0982376460731</v>
       </c>
       <c r="X22" t="n">
-        <v>157.7509537125588</v>
+        <v>157.3276290061944</v>
       </c>
       <c r="Y22" t="n">
-        <v>44.37320992131234</v>
+        <v>43.53981308022023</v>
       </c>
       <c r="Z22" t="n">
-        <v>585.0829960394502</v>
+        <v>583.6867257502295</v>
       </c>
     </row>
     <row r="23">
@@ -2332,13 +2332,13 @@
         <v>29.74982865825887</v>
       </c>
       <c r="E23" t="n">
-        <v>40.10610650344454</v>
+        <v>40.06265551792472</v>
       </c>
       <c r="F23" t="n">
-        <v>38.09334657860407</v>
+        <v>38.05207621867904</v>
       </c>
       <c r="G23" t="n">
-        <v>51.77214691795154</v>
+        <v>51.71605693559763</v>
       </c>
       <c r="H23" t="n">
         <v>49.69145709186481</v>
@@ -2362,25 +2362,25 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>43.89111634717568</v>
+        <v>43.67845028762508</v>
       </c>
       <c r="P23" t="n">
-        <v>29.18231050910368</v>
+        <v>29.00747621819678</v>
       </c>
       <c r="Q23" t="n">
         <v>50</v>
       </c>
       <c r="R23" t="n">
-        <v>21.98215322735031</v>
+        <v>21.65887090778737</v>
       </c>
       <c r="S23" t="n">
-        <v>21.40570173330585</v>
+        <v>21.09089704440005</v>
       </c>
       <c r="T23" t="n">
         <v>60.30096381462343</v>
       </c>
       <c r="U23" t="n">
-        <v>129.9716000000002</v>
+        <v>129.8307886722014</v>
       </c>
       <c r="V23" t="n">
         <v>147.8046749336513</v>
@@ -2389,13 +2389,13 @@
         <v>45.14391904070973</v>
       </c>
       <c r="X23" t="n">
-        <v>157.5734268562794</v>
+        <v>157.1859265058219</v>
       </c>
       <c r="Y23" t="n">
-        <v>43.38785496065617</v>
+        <v>42.74976795218742</v>
       </c>
       <c r="Z23" t="n">
-        <v>584.1824396059201</v>
+        <v>583.0160409191951</v>
       </c>
     </row>
     <row r="24">
@@ -2414,13 +2414,13 @@
         <v>29.83810282876176</v>
       </c>
       <c r="E24" t="n">
-        <v>40.09481444179709</v>
+        <v>40.05080953987845</v>
       </c>
       <c r="F24" t="n">
-        <v>38.11375475444166</v>
+        <v>38.0719241071854</v>
       </c>
       <c r="G24" t="n">
-        <v>51.76303080376142</v>
+        <v>51.70621978903935</v>
       </c>
       <c r="H24" t="n">
         <v>49.05122120630682</v>
@@ -2444,25 +2444,25 @@
         <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>44.22439834206929</v>
+        <v>43.97514689026387</v>
       </c>
       <c r="P24" t="n">
-        <v>28.96436508607037</v>
+        <v>28.77214945965358</v>
       </c>
       <c r="Q24" t="n">
         <v>50</v>
       </c>
       <c r="R24" t="n">
-        <v>22.26406064933875</v>
+        <v>21.90241665524597</v>
       </c>
       <c r="S24" t="n">
-        <v>21.73236683098933</v>
+        <v>21.3793593511035</v>
       </c>
       <c r="T24" t="n">
         <v>60.49220818291731</v>
       </c>
       <c r="U24" t="n">
-        <v>129.9716000000002</v>
+        <v>129.8289534361032</v>
       </c>
       <c r="V24" t="n">
         <v>145.9051374384241</v>
@@ -2471,13 +2471,13 @@
         <v>45.21352827295661</v>
       </c>
       <c r="X24" t="n">
-        <v>157.6887634281397</v>
+        <v>157.2472963499175</v>
       </c>
       <c r="Y24" t="n">
-        <v>43.99642748032809</v>
+        <v>43.28177600634947</v>
       </c>
       <c r="Z24" t="n">
-        <v>583.2676648027659</v>
+        <v>581.9688996866682</v>
       </c>
     </row>
     <row r="25">
@@ -2496,13 +2496,13 @@
         <v>30.11316183250342</v>
       </c>
       <c r="E25" t="n">
-        <v>40.0831970982069</v>
+        <v>40.03725828783737</v>
       </c>
       <c r="F25" t="n">
-        <v>38.12062205377774</v>
+        <v>38.07693252413752</v>
       </c>
       <c r="G25" t="n">
-        <v>51.76778084801553</v>
+        <v>51.70845049415672</v>
       </c>
       <c r="H25" t="n">
         <v>48.75877657397292</v>
@@ -2526,25 +2526,25 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>44.41877415118671</v>
+        <v>44.17398696338672</v>
       </c>
       <c r="P25" t="n">
-        <v>28.69225756288314</v>
+        <v>28.50887757975601</v>
       </c>
       <c r="Q25" t="n">
         <v>50</v>
       </c>
       <c r="R25" t="n">
-        <v>22.40362105746585</v>
+        <v>22.05336159966907</v>
       </c>
       <c r="S25" t="n">
-        <v>21.9066926826982</v>
+        <v>21.5642022307538</v>
       </c>
       <c r="T25" t="n">
         <v>61.03577604214973</v>
       </c>
       <c r="U25" t="n">
-        <v>129.9716000000002</v>
+        <v>129.8226413061316</v>
       </c>
       <c r="V25" t="n">
         <v>145.0369519565465</v>
@@ -2553,13 +2553,13 @@
         <v>45.15398705497384</v>
       </c>
       <c r="X25" t="n">
-        <v>157.6110317140698</v>
+        <v>157.1828645431427</v>
       </c>
       <c r="Y25" t="n">
-        <v>44.31031374016405</v>
+        <v>43.61756383042287</v>
       </c>
       <c r="Z25" t="n">
-        <v>583.1196605079042</v>
+        <v>581.8497847333673</v>
       </c>
     </row>
   </sheetData>
